--- a/data/trans_orig/P57_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71866</t>
+          <t>72663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104876</t>
+          <t>105827</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>73653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105875</t>
+          <t>106202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154308</t>
+          <t>153352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199944</t>
+          <t>199546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>187955</t>
+          <t>187004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220965</t>
+          <t>220168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182828</t>
+          <t>182501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215267</t>
+          <t>215050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>381590</t>
+          <t>381988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>427226</t>
+          <t>428182</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57198</t>
+          <t>57408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>90062</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>61653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94905</t>
+          <t>96285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127816</t>
+          <t>126760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171978</t>
+          <t>174865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410273</t>
+          <t>409307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442171</t>
+          <t>441961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426268</t>
+          <t>424888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461096</t>
+          <t>459520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>848564</t>
+          <t>845677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892726</t>
+          <t>893782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>18263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>37724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>66384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63519</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98829</t>
+          <t>96953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279628</t>
+          <t>279976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298411</t>
+          <t>299437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>268976</t>
+          <t>269925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>297086</t>
+          <t>297269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>555180</t>
+          <t>557056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>590490</t>
+          <t>590184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>44329</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75573</t>
+          <t>72846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91359</t>
+          <t>90468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126612</t>
+          <t>127110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143237</t>
+          <t>142147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192487</t>
+          <t>191943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291367</t>
+          <t>294094</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320517</t>
+          <t>322611</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258261</t>
+          <t>257763</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293514</t>
+          <t>294405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>559870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>608576</t>
+          <t>609666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60203</t>
+          <t>59663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86817</t>
+          <t>86497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76491</t>
+          <t>77492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105371</t>
+          <t>106063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>144007</t>
+          <t>143648</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183943</t>
+          <t>184662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124404</t>
+          <t>124724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151018</t>
+          <t>151558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113216</t>
+          <t>112524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142096</t>
+          <t>141095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245865</t>
+          <t>245146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285801</t>
+          <t>286160</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,58%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62398</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>46114</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73855</t>
+          <t>72643</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90312</t>
+          <t>90957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129635</t>
+          <t>126829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200725</t>
+          <t>199330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225452</t>
+          <t>224941</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>198258</t>
+          <t>199470</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226504</t>
+          <t>225999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>405601</t>
+          <t>408407</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>444924</t>
+          <t>444279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87649</t>
+          <t>88507</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128013</t>
+          <t>125965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118241</t>
+          <t>120780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163407</t>
+          <t>166404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221069</t>
+          <t>221097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>278673</t>
+          <t>280761</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>522953</t>
+          <t>525001</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>563317</t>
+          <t>562459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>518785</t>
+          <t>515788</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>563951</t>
+          <t>561412</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1054485</t>
+          <t>1052397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1112089</t>
+          <t>1112061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132486</t>
+          <t>132362</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177734</t>
+          <t>176891</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183068</t>
+          <t>184038</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>236974</t>
+          <t>239819</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>331008</t>
+          <t>330277</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>397328</t>
+          <t>399265</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>600849</t>
+          <t>601692</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>646097</t>
+          <t>646221</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>587180</t>
+          <t>584335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>641086</t>
+          <t>640116</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1205409</t>
+          <t>1203472</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1271729</t>
+          <t>1272460</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>580009</t>
+          <t>583378</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>668542</t>
+          <t>673888</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>780032</t>
+          <t>774090</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>882980</t>
+          <t>877276</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1386274</t>
+          <t>1388120</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1529294</t>
+          <t>1525323</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2712191</t>
+          <t>2706845</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2800724</t>
+          <t>2797355</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2645124</t>
+          <t>2650828</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2748072</t>
+          <t>2754014</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5379543</t>
+          <t>5383514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5522563</t>
+          <t>5520717</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28359</t>
+          <t>27223</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>27599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47722</t>
+          <t>48579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283084</t>
+          <t>284220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299972</t>
+          <t>300173</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264793</t>
+          <t>264641</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276572</t>
+          <t>277001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>553355</t>
+          <t>552498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573676</t>
+          <t>573478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18075</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45758</t>
+          <t>44520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>41302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>44662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79404</t>
+          <t>77381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472632</t>
+          <t>473870</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500315</t>
+          <t>500916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469832</t>
+          <t>469935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488032</t>
+          <t>487906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950222</t>
+          <t>952245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>984616</t>
+          <t>984964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49425</t>
+          <t>49541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75900</t>
+          <t>75020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60362</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86145</t>
+          <t>84362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115312</t>
+          <t>117254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152863</t>
+          <t>151473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238403</t>
+          <t>239283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264878</t>
+          <t>264762</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261413</t>
+          <t>263196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287196</t>
+          <t>287163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>508998</t>
+          <t>510388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>546549</t>
+          <t>544607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>27707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63810</t>
+          <t>64938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62725</t>
+          <t>61605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107661</t>
+          <t>107891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252436</t>
+          <t>251371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>278260</t>
+          <t>277793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>401162</t>
+          <t>400034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>439361</t>
+          <t>436083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662811</t>
+          <t>662581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>707747</t>
+          <t>708867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159875</t>
+          <t>159702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170365</t>
+          <t>170432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182158</t>
+          <t>182474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192697</t>
+          <t>192762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346275</t>
+          <t>346599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361036</t>
+          <t>360722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46666</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69152</t>
+          <t>68852</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48614</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99911</t>
+          <t>100623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129737</t>
+          <t>130316</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200484</t>
+          <t>200784</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222970</t>
+          <t>223276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188757</t>
+          <t>187873</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208126</t>
+          <t>206711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>396639</t>
+          <t>396060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>426465</t>
+          <t>425753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43842</t>
+          <t>44329</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73992</t>
+          <t>73477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116255</t>
+          <t>116037</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84625</t>
+          <t>89399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171603</t>
+          <t>172572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>549528</t>
+          <t>550043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>579678</t>
+          <t>579191</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>731123</t>
+          <t>731341</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>811118</t>
+          <t>807070</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1299295</t>
+          <t>1298326</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386273</t>
+          <t>1381499</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67530</t>
+          <t>70327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>220371</t>
+          <t>222160</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>225023</t>
+          <t>224558</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>267275</t>
+          <t>266631</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246023</t>
+          <t>245709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>478984</t>
+          <t>482950</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>707729</t>
+          <t>705940</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>860570</t>
+          <t>857773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>448813</t>
+          <t>449457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>491065</t>
+          <t>491530</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1165205</t>
+          <t>1161239</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1398166</t>
+          <t>1398480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>337766</t>
+          <t>331725</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>478937</t>
+          <t>479683</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>467756</t>
+          <t>460815</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>632423</t>
+          <t>630378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>872095</t>
+          <t>887320</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1086800</t>
+          <t>1086718</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2970696</t>
+          <t>2969950</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3111867</t>
+          <t>3117908</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3007893</t>
+          <t>3009938</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3172560</t>
+          <t>3179501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6003149</t>
+          <t>6003231</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6217854</t>
+          <t>6202629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72663</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105827</t>
+          <t>105101</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73653</t>
+          <t>74501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106202</t>
+          <t>107292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153352</t>
+          <t>156308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199546</t>
+          <t>200834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>187004</t>
+          <t>187730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220168</t>
+          <t>220531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182501</t>
+          <t>181411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215050</t>
+          <t>214202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>381988</t>
+          <t>380700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>428182</t>
+          <t>425226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57408</t>
+          <t>57762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90062</t>
+          <t>89591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61653</t>
+          <t>62959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96285</t>
+          <t>97241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>126760</t>
+          <t>124769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174865</t>
+          <t>173980</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409307</t>
+          <t>409778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441961</t>
+          <t>441607</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424888</t>
+          <t>423932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459520</t>
+          <t>458214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>845677</t>
+          <t>846562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>893782</t>
+          <t>895773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37724</t>
+          <t>37886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39040</t>
+          <t>39203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66384</t>
+          <t>67130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63825</t>
+          <t>62409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>96434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279976</t>
+          <t>279814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299437</t>
+          <t>298895</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269925</t>
+          <t>269179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>297269</t>
+          <t>297106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>557056</t>
+          <t>557575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>590184</t>
+          <t>591600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72846</t>
+          <t>72604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90468</t>
+          <t>88913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127110</t>
+          <t>126237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142147</t>
+          <t>143546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191943</t>
+          <t>189421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>294094</t>
+          <t>294336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322611</t>
+          <t>321696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257763</t>
+          <t>258636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294405</t>
+          <t>295960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>559870</t>
+          <t>562392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>609666</t>
+          <t>608267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59663</t>
+          <t>58739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86497</t>
+          <t>86340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77492</t>
+          <t>77475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106063</t>
+          <t>104796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143648</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>184662</t>
+          <t>183544</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124724</t>
+          <t>124881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151558</t>
+          <t>152482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112524</t>
+          <t>113791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141095</t>
+          <t>141112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245146</t>
+          <t>246264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286160</t>
+          <t>285982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63793</t>
+          <t>62508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46114</t>
+          <t>46379</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72643</t>
+          <t>73726</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,47 +2496,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>107644</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>90740</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>127568</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>16,95%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>26,7%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>107644</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>90957</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>126829</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>20,11%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199330</t>
+          <t>200615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224941</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>199470</t>
+          <t>198387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225999</t>
+          <t>225734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,47 +2609,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>427592</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>407668</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>444496</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>79,89%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>76,17%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>83,05%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>427592</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>408407</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>444279</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>79,89%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>76,3%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88507</t>
+          <t>88684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125965</t>
+          <t>126134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120780</t>
+          <t>120411</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166404</t>
+          <t>164854</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221097</t>
+          <t>219303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>280761</t>
+          <t>278887</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>525001</t>
+          <t>524832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>562459</t>
+          <t>562282</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>515788</t>
+          <t>517338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>561412</t>
+          <t>561781</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1052397</t>
+          <t>1054271</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1112061</t>
+          <t>1113855</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132362</t>
+          <t>133671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176891</t>
+          <t>175810</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184038</t>
+          <t>185767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>239819</t>
+          <t>236741</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>330277</t>
+          <t>327674</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>399265</t>
+          <t>400006</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>601692</t>
+          <t>602773</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>646221</t>
+          <t>644912</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>584335</t>
+          <t>587413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>640116</t>
+          <t>638387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1203472</t>
+          <t>1202731</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1272460</t>
+          <t>1275063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,56%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>583378</t>
+          <t>584516</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>673888</t>
+          <t>679576</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>774090</t>
+          <t>777164</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>877276</t>
+          <t>880662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1388120</t>
+          <t>1388057</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1525323</t>
+          <t>1525720</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2706845</t>
+          <t>2701157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2797355</t>
+          <t>2796217</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2650828</t>
+          <t>2647442</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2754014</t>
+          <t>2750940</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5383514</t>
+          <t>5383117</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5520717</t>
+          <t>5520780</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27223</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27599</t>
+          <t>29354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48579</t>
+          <t>49156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>293299</t>
+          <t>301041</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284220</t>
+          <t>292735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300173</t>
+          <t>307831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>270875</t>
+          <t>295817</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264641</t>
+          <t>288480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277001</t>
+          <t>301205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>564173</t>
+          <t>596858</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552498</t>
+          <t>585750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573478</t>
+          <t>605552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28414</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44520</t>
+          <t>45448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23331</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41302</t>
+          <t>43905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>59621</t>
+          <t>61926</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44662</t>
+          <t>47971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77381</t>
+          <t>81803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>489976</t>
+          <t>501355</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>485199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500916</t>
+          <t>512082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>480030</t>
+          <t>510004</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469935</t>
+          <t>498733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487906</t>
+          <t>517154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>970005</t>
+          <t>1011359</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952245</t>
+          <t>991482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>984964</t>
+          <t>1025314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511237</t>
+          <t>542638</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511237</t>
+          <t>542638</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511237</t>
+          <t>542638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029626</t>
+          <t>1073285</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029626</t>
+          <t>1073285</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029626</t>
+          <t>1073285</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>61468</t>
+          <t>64004</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49541</t>
+          <t>51302</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75020</t>
+          <t>77554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>72370</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60395</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84362</t>
+          <t>83842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,22 +4805,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>133839</t>
+          <t>136359</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117254</t>
+          <t>118563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151473</t>
+          <t>154382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>252835</t>
+          <t>250287</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239283</t>
+          <t>236737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264762</t>
+          <t>262989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>275188</t>
+          <t>282397</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263196</t>
+          <t>270911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287163</t>
+          <t>293212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,27 +4918,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>528022</t>
+          <t>532685</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>510388</t>
+          <t>514662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>544607</t>
+          <t>550481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314303</t>
+          <t>314291</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314303</t>
+          <t>314291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314303</t>
+          <t>314291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>354753</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>354753</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>354753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>661861</t>
+          <t>669044</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>661861</t>
+          <t>669044</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>661861</t>
+          <t>669044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>43402</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54129</t>
+          <t>59899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46964</t>
+          <t>51336</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>39591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64938</t>
+          <t>64870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>85488</t>
+          <t>94739</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61605</t>
+          <t>79116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107891</t>
+          <t>115555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>266976</t>
+          <t>321964</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251371</t>
+          <t>305467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>277793</t>
+          <t>334893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>418008</t>
+          <t>358553</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>400034</t>
+          <t>345019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>436083</t>
+          <t>370298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>684984</t>
+          <t>680515</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662581</t>
+          <t>659699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708867</t>
+          <t>696138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>305500</t>
+          <t>365366</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>305500</t>
+          <t>365366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>305500</t>
+          <t>365366</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>464972</t>
+          <t>409889</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>464972</t>
+          <t>409889</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>464972</t>
+          <t>409889</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>770472</t>
+          <t>775254</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>770472</t>
+          <t>775254</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>770472</t>
+          <t>775254</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24234</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>31257</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165904</t>
+          <t>191158</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159702</t>
+          <t>184504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170432</t>
+          <t>196293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>188289</t>
+          <t>206895</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182474</t>
+          <t>200559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192762</t>
+          <t>211464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>354193</t>
+          <t>398054</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346599</t>
+          <t>389015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>360722</t>
+          <t>405135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385450</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385450</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385450</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57348</t>
+          <t>60348</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46360</t>
+          <t>49775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68852</t>
+          <t>73131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58057</t>
+          <t>60491</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50029</t>
+          <t>51270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68867</t>
+          <t>70737</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>115405</t>
+          <t>120839</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100623</t>
+          <t>107095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130316</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>212288</t>
+          <t>210359</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200784</t>
+          <t>197576</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223276</t>
+          <t>220932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>198683</t>
+          <t>202946</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187873</t>
+          <t>192700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206711</t>
+          <t>212167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>410971</t>
+          <t>413306</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>396060</t>
+          <t>397625</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>425753</t>
+          <t>427050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>263437</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>263437</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>263437</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526376</t>
+          <t>534145</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526376</t>
+          <t>534145</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526376</t>
+          <t>534145</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>57478</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>54042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>86812</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>82673</t>
+          <t>101669</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>85174</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116037</t>
+          <t>119676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>140152</t>
+          <t>169658</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89399</t>
+          <t>144679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172572</t>
+          <t>192739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>566042</t>
+          <t>650879</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>550043</t>
+          <t>632056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>579191</t>
+          <t>664826</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>764705</t>
+          <t>668350</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>731341</t>
+          <t>650343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>807070</t>
+          <t>684845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1330746</t>
+          <t>1319229</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1298326</t>
+          <t>1296148</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1381499</t>
+          <t>1344208</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623520</t>
+          <t>718868</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623520</t>
+          <t>718868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623520</t>
+          <t>718868</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847378</t>
+          <t>770019</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847378</t>
+          <t>770019</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847378</t>
+          <t>770019</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470898</t>
+          <t>1488887</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470898</t>
+          <t>1488887</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470898</t>
+          <t>1488887</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>155662</t>
+          <t>174462</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70327</t>
+          <t>154644</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>222160</t>
+          <t>201731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,32 +6485,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>245398</t>
+          <t>283732</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224558</t>
+          <t>258350</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266631</t>
+          <t>306713</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>401060</t>
+          <t>458194</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>245709</t>
+          <t>423858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>482950</t>
+          <t>493104</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>772438</t>
+          <t>622943</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>705940</t>
+          <t>595674</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>857773</t>
+          <t>642761</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,32 +6598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>470690</t>
+          <t>545798</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>449457</t>
+          <t>522817</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>491530</t>
+          <t>571180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1243129</t>
+          <t>1168741</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1161239</t>
+          <t>1133831</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1398480</t>
+          <t>1203077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797405</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797405</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797405</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716088</t>
+          <t>829530</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716088</t>
+          <t>829530</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716088</t>
+          <t>829530</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644189</t>
+          <t>1626935</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644189</t>
+          <t>1626935</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644189</t>
+          <t>1626935</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>429876</t>
+          <t>471807</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>331725</t>
+          <t>430826</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>479683</t>
+          <t>514378</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>573850</t>
+          <t>641958</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>460815</t>
+          <t>599754</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>630378</t>
+          <t>677803</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1003726</t>
+          <t>1113764</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>887320</t>
+          <t>1061579</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1086718</t>
+          <t>1174508</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3019757</t>
+          <t>3049986</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2969950</t>
+          <t>3007415</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3117908</t>
+          <t>3090967</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3066466</t>
+          <t>3070760</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3009938</t>
+          <t>3034915</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3179501</t>
+          <t>3112964</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6086223</t>
+          <t>6120747</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6003231</t>
+          <t>6060003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6202629</t>
+          <t>6172932</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
